--- a/scripts/WOs List PEXT.xlsx
+++ b/scripts/WOs List PEXT.xlsx
@@ -157,7 +157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AI15"/>
+  <dimension ref="A1:AI27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="24" max="24" width="26.0" customWidth="true"/>
@@ -377,17 +377,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CM-20260909-00000167</t>
+          <t>CM-20260913-00000295</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INC-20260909-00004101</t>
+          <t>INC-20260913-00006712</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-09 13:07:36</t>
+          <t>2026-09-13 21:27:17</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -407,7 +407,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2601210001-Loss of signal</t>
+          <t>235-ETH_LOS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -422,22 +422,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0130387</t>
+          <t>0135587</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0130387_LM_Lurin</t>
+          <t>0135587_LM_Monserrate</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>CAIDA</t>
+          <t>CORTE</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -447,7 +447,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>04:24:23</t>
+          <t>11:34:28</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>LURIN</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -472,12 +472,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Álvaro Ballarta</t>
+          <t>Edgar Soto</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-09 13:09:16</t>
+          <t>2026-09-13 21:28:33</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -542,44 +542,44 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CM-20260909-00000141</t>
+          <t>CM-20260913-00000278</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INC-20260909-00003294</t>
+          <t>INC-20260913-00006137</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-09 11:35:20</t>
+          <t>2026-09-13 19:46:08</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-13 20:39:25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-09 16:39:16</t>
+          <t>2026-09-13 19:57:23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0130415</t>
+          <t>0130119</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0130415_LM_Candia</t>
+          <t>0130119_LM_Estadio_Alianza</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>05:56:40</t>
+          <t>13:01:32</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>SANTIAGO DE SURCO</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>inprocess</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-09 11:36:59</t>
+          <t>2026-09-13 20:01:29</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>arrive</t>
+          <t>create</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>JHONATAN VICENTE ANASTACIO SAIRUTUPAC</t>
+          <t/>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-13 20:39:25</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -719,34 +719,34 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CM-20260909-00000105</t>
+          <t>CM-20260913-00000265</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INC-20260909-00002322</t>
+          <t>INC-20260913-00004502</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-09 09:12:46</t>
+          <t>2026-09-13 19:07:32</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-09 15:08:00</t>
+          <t>2026-09-14 07:00:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:51</t>
+          <t>2026-09-14 07:00:00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2506110004-Cell Unavailable Transporte</t>
+          <t>235-ETH_LOS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FO Cut</t>
+          <t>prueba</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -776,22 +776,22 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0135249</t>
+          <t>0130387</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0135249_LM_Merino_Reyna</t>
+          <t>0130387_LM_Lurin</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>CAIDA</t>
+          <t>CORTE</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>08:20:06</t>
+          <t>13:53:31</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>CARABAYLLO</t>
+          <t>LURIN</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,12 +826,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>César Zuñiga</t>
+          <t>Álvaro Ballarta</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-09 09:13:33</t>
+          <t>2026-09-13 19:09:30</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -841,12 +841,9 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Operator: user:gaquije.cobra
-Complete time: 
-Description: 
-Operator: user:cesil.bustamante
-Complete time: 2026-09-09 15:02:41
-Description: fibra partida en medio tramo</t>
+          <t>Operator: user:bcastillod
+Complete time: 2026-09-14 06:57:02
+Description: hilo partido, en mufa</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -866,7 +863,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>GABRIEL STTEFFANO AQUIJE CORNEJO</t>
+          <t>ANDY JAVIER RODAS VILLAJUAN</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -876,17 +873,17 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-09-09 15:02:42</t>
+          <t>2026-09-14 06:57:03</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2026-09-09 15:04:27</t>
+          <t>2026-09-14 06:57:41</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-09-09 15:04:28</t>
+          <t>2026-09-14 06:57:43</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -901,7 +898,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -913,32 +910,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CM-20260908-00000205</t>
+          <t>CM-20260913-00000226</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INC-20260908-00005443</t>
+          <t>INC-20260913-00004824</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-08 15:27:41</t>
+          <t>2026-09-13 15:46:30</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-08 18:02:00</t>
+          <t/>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>running</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-08 18:02:00</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -948,7 +945,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FO Cut</t>
+          <t/>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -958,17 +955,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0130176</t>
+          <t>013253025</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0130176_LM_Huanuco</t>
+          <t>013253025_LM_PS_UniversidadTecLimaSur</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -978,12 +975,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>02:02:55</t>
+          <t>17:15:03</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -998,22 +995,22 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>LA VICTORIA</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>inprocess</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Edwin Oscco</t>
+          <t>Álvaro Ballarta</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-08 15:30:44</t>
+          <t>2026-09-13 15:47:58</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1023,9 +1020,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator: user:bcastillod
-Complete time: 2026-09-08 17:57:34
-Description: Corte de fo, múltiples Llamadas </t>
+          <t>'-</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1040,12 +1035,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>close</t>
+          <t>depart</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RUBEN HILDO MERCADO CAMARGO</t>
+          <t>JHONATAN VICENTE ANASTACIO SAIRUTUPAC</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1055,17 +1050,17 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-09-08 17:57:36</t>
+          <t/>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2026-09-08 17:58:23</t>
+          <t/>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-09-08 17:58:24</t>
+          <t/>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1075,7 +1070,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t/>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1092,37 +1087,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CM-20260908-00000169</t>
+          <t>CM-20260913-00000204</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INC-20260908-00004560</t>
+          <t>INC-20260913-00004410</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-08 13:44:55</t>
+          <t>2026-09-13 14:26:48</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-08 14:55:08</t>
+          <t/>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>running</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-08 13:53:38</t>
+          <t/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2505070002-Input LOS</t>
+          <t>235-ETH_LOS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1137,17 +1132,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0130011</t>
+          <t>0136114</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0130011_LM_Lurigancho</t>
+          <t>0136114_LM_Jesus_Redentor</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1157,12 +1152,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>03:47:40</t>
+          <t>18:35:29</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1177,22 +1172,22 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>dispatched</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Edgar Soto</t>
+          <t>Yoshua Quispe</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:59</t>
+          <t>2026-09-13 14:27:32</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1217,12 +1212,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>dispatch</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t/>
+          <t>GERSON ANDRE VIVANCO DIESTRA</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1247,7 +1242,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-09-08 14:55:09</t>
+          <t/>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1257,7 +1252,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1269,42 +1264,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CM-20260908-00000137</t>
+          <t>CM-20260913-00000111</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t/>
+          <t>INC-20260912-00007617</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-12 20:18:11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-13 11:18:04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t/>
+          <t>completed</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-13 10:31:04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2507160001-ETH_LOS_CAIDA</t>
+          <t>235-ETH_LOS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t/>
+          <t>FO Cut</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1314,32 +1309,32 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0136588</t>
+          <t>0130015</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0136588_LM_RepFO_Olguin_Amer</t>
+          <t>0130015_LM_Huayucari</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>CAIDA</t>
+          <t>CORTE</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>05:11:40</t>
+          <t>23:20:15</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1354,22 +1349,22 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>SANTIAGO DE SURCO</t>
+          <t>ATE</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>unscheduled</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Edwin Oscco</t>
+          <t>Martín Figueroa</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-08 12:21:59</t>
+          <t>2026-09-13 09:42:46</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1379,7 +1374,10 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t>Operator: user:Yuliza.Jaimes
+Complete time: 2026-09-13 11:14:12
+Description: se encontro hilo averiado en tramo
+solución se realizo cambio de cuenta entre mufas en tramo</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1394,12 +1392,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>close</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t/>
+          <t>JUAN JOSE CARRION QUISPE</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1409,17 +1407,17 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-13 11:14:14</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-13 11:14:58</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-13 11:14:59</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1446,42 +1444,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CM-20260908-00000104</t>
+          <t>CM-20260913-00000107</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>INC-20260908-00003064</t>
+          <t>INC-20260913-00002313</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-08 10:40:49</t>
+          <t>2026-09-13 09:35:53</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14 01:22:01</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-08 17:31:26</t>
+          <t>2026-09-13 19:56:29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2506110004-Cell Unavailable Transporte</t>
+          <t>2601500-ETH_LOS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t/>
+          <t>FO Cut</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1491,32 +1489,32 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0135261</t>
+          <t>0130015</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0135261_LM_Los_Incas</t>
+          <t>0130015_LM_Huayucari</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>CAIDA</t>
+          <t>CORTE</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>06:52:01</t>
+          <t>23:26:28</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1531,22 +1529,22 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>COMAS</t>
+          <t>ATE</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>dispatched</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>César Zuñiga</t>
+          <t>Martín Figueroa</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-08 10:41:38</t>
+          <t>2026-09-13 09:36:33</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1556,7 +1554,16 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t xml:space="preserve">Operator: user:Jpachecom.cobra
+Complete time: 
+Description: 
+Operator: user:jcarrion.cobra
+Complete time: 
+Description: 
+Operator: user:System
+Complete time: 2026-09-14 01:18:50
+Description: causa : ruptura de fibra por camión de gran altura 
+solución: tendido de fibra y creación de dos bandejas de averia  se deja con señal ok tendido de 100 metros </t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1571,12 +1578,12 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>dispatch</t>
+          <t>close</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>GERSON ANDRE VIVANCO DIESTRA</t>
+          <t>JUAN JOSE CARRION QUISPE</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1586,17 +1593,17 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14 01:18:55</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14 01:20:00</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14 01:20:03</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1611,54 +1618,54 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CM-20260908-00000087</t>
+          <t>CM-20260912-00000296</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>INC-20260908-00002814</t>
+          <t>INC-20260912-00008409</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-08 10:12:44</t>
+          <t>2026-09-12 23:13:30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-08 14:34:01</t>
+          <t/>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>running</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-08 13:31:47</t>
+          <t/>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2506110004-Cell Unavailable Transporte</t>
+          <t>2601500-ETH_LOS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FO Cut</t>
+          <t/>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1668,22 +1675,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0135249</t>
+          <t>0130176</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0135249_LM_Merino_Reyna</t>
+          <t>0130176_LM_Huanuco</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>CAIDA</t>
+          <t>CORTE</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1693,7 +1700,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>07:20:07</t>
+          <t>09:41:44</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1708,34 +1715,43 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>CARABAYLLO</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>inprocess</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>César Zuñiga</t>
+          <t>Edwin Oscco</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-08 10:13:32</t>
+          <t>2026-09-12 23:21:17</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t xml:space="preserve">Type: PAUSE
+Reason: Restricciones por temas de seguridad personal
+Operation time: 2026-09-13 16:31:06
+Creator: vcauti.cobra
+Description: por accesos y zona peligrosa
+Type: RESUME
+Reason: 
+Operation time: 2026-09-14 08:39:41
+Creator: rmercado.cobra
+Description: Se reanuda labores </t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator: user:cesil.bustamante
-Complete time: 2026-09-08 14:29:27
-Description: Fo reparada, empalmada </t>
+          <t xml:space="preserve">Operator: user:rmercado.cobra
+Complete time: 
+Description: </t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1750,7 +1766,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>close</t>
+          <t>depart</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1765,17 +1781,17 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-09-08 14:29:30</t>
+          <t/>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2026-09-08 14:30:12</t>
+          <t/>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-09-08 14:30:13</t>
+          <t/>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1790,7 +1806,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -1802,22 +1818,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CM-20260907-00000223</t>
+          <t>CM-20260912-00000266</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>INC-20260907-00005974</t>
+          <t>INC-20260912-00007617</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-07 18:44:42</t>
+          <t>2026-09-12 20:18:11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-08 11:10:00</t>
+          <t>2026-09-13 11:18:04</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1827,7 +1843,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-08 11:10:01</t>
+          <t>2026-09-13 10:31:04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1837,7 +1853,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FO Cut</t>
+          <t/>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1847,12 +1863,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0130045</t>
+          <t>0162762</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0130045_LM_Shell</t>
+          <t>0162762_LM_HB_Ate_AMT</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1872,7 +1888,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>22:46:46</t>
+          <t>12:41:07</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1887,46 +1903,32 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>MIRAFLORES</t>
+          <t>ATE</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Edwin Oscco</t>
+          <t>Martin Figueroa</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-09-07 18:46:53</t>
+          <t>2026-09-12 20:21:54</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Type: PAUSE
-Reason: Restricciones de acceso por parte de terceros notificada a ENTEL
-Operation time: 2026-09-07 22:18:48
-Creator: vcauti.cobra
-Description: serenasgo no permite el trabajo hora  de trabajo permitido 9:00 a 17:00 hrs
-Type: RESUME
-Reason: 
-Operation time: 2026-09-08 11:04:50
-Creator: gvivanco.cobra
-Description: hilo alimentador roto</t>
+          <t>'-</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator: user:gvivanco.cobra
-Complete time: 
-Description: 
-Operator: user:bcastillod
-Complete time: 2026-09-08 11:06:32
-Description: se encuentra hilo cortado a 1300 metros </t>
+          <t>'-</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1941,12 +1943,12 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>close</t>
+          <t>create</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>GERSON ANDRE VIVANCO DIESTRA</t>
+          <t/>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1956,27 +1958,27 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-09-08 11:06:34</t>
+          <t/>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2026-09-08 11:07:18</t>
+          <t/>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2026-09-08 11:07:19</t>
+          <t/>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-13 09:41:28</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -1993,22 +1995,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CM-20260907-00000194</t>
+          <t>CM-20260912-00000265</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>INC-20260907-00005030</t>
+          <t>INC-20260912-00007617</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-07 15:49:02</t>
+          <t>2026-09-12 20:18:11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-07 18:08:09</t>
+          <t>2026-09-13 11:18:04</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2018,7 +2020,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-07 18:08:09</t>
+          <t>2026-09-13 10:31:04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2028,7 +2030,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Rectifier</t>
+          <t/>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2038,12 +2040,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0130176</t>
+          <t>0162762</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0130176_LM_Huanuco</t>
+          <t>0162762_LM_HB_Ate_AMT</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2058,12 +2060,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>01:41:44</t>
+          <t>12:42:28</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2078,22 +2080,22 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>LA VICTORIA</t>
+          <t>ATE</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Edwin Oscco</t>
+          <t>Martin Figueroa</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-07 15:51:55</t>
+          <t>2026-09-12 20:20:33</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -2103,9 +2105,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Operator: user:bcastillod
-Complete time: 2026-09-07 18:04:27
-Description: atenuación en el empalme a 166 mtrs en una mufa</t>
+          <t>'-</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>close</t>
+          <t>create</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>GERSON ANDRE VIVANCO DIESTRA</t>
+          <t/>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -2135,59 +2135,59 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-09-07 18:04:29</t>
+          <t/>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2026-09-07 18:05:23</t>
+          <t/>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2026-09-07 18:05:24</t>
+          <t/>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-13 09:41:54</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CM-20260907-00000078</t>
+          <t>CM-20260912-00000244</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INC-20260907-00002481</t>
+          <t>INC-20260912-00006953</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-07 09:50:11</t>
+          <t>2026-09-12 18:37:56</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-07 18:14:00</t>
+          <t>2026-09-13 09:40:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2197,12 +2197,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-07 18:14:00</t>
+          <t>2026-09-13 09:29:47</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>12793-ETH_LINK_DOWN</t>
+          <t>235-ETH_LOS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2212,37 +2212,37 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t/>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0130266</t>
+          <t>0130522</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0130266_LM_Bausate</t>
+          <t>0130522_LM_IB_MSO_San_Borja</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0+</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>CAIDA</t>
+          <t>CORTE</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>07:42:35</t>
+          <t>14:14:40</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>LA VICTORIA</t>
+          <t>SAN BORJA</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Edwin Oscco</t>
+          <t>Álvaro Ballarta</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-09-07 09:51:04</t>
+          <t>2026-09-12 18:48:21</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2282,9 +2282,9 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator: user:jose.cuya
-Complete time: 2026-09-07 18:10:29
-Description: atenuación a 166 mtrs, se rehace el empalme en mufa </t>
+          <t xml:space="preserve">Operator: user:Boris.Chivilchez
+Complete time: 2026-09-13 09:31:17
+Description: se empalma hilo </t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>GERSON ANDRE VIVANCO DIESTRA</t>
+          <t>VICTOR WILLIAM CAUTI AGUIRRE</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2314,17 +2314,17 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-09-07 18:10:31</t>
+          <t>2026-09-13 09:31:21</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2026-09-07 18:10:56</t>
+          <t>2026-09-13 09:37:50</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2026-09-07 18:10:58</t>
+          <t>2026-09-13 09:37:52</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -2351,545 +2351,2684 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CM-20260907-00000076</t>
+          <t>CM-20260912-00000238</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INC-20260907-00002334</t>
+          <t>INC-20260912-00006860</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-07 09:25:16</t>
+          <t>2026-09-12 18:23:31</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-12 18:47:01</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>cancel</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>235-ETH_LOS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0130283</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0130283_LM_Quechuas</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>CORTE</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>14:38:03</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>canceled</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Martín Figueroa</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2026-09-12 18:24:58</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>2026-09-12 18:47:01</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CM-20260912-00000231</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>INC-20260912-00006553</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-09-12 17:32:40</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-09-13 09:56:00</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-13 09:56:00</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>235-ETH_LOS</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>FO Cut</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0130373</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0130373_LM_Carabayllo</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>CORTE</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>15:27:36</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>PUENTE PIEDRA</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Edgar Soto</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2026-09-12 17:35:25</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Operator: user:Jpachecom.cobra
+Complete time: 
+Description: 
+Operator: user:gvivanco.cobra
+Complete time: 
+Description: 
+Operator: user:Boris.Chivilchez
+Complete time: 2026-09-13 09:52:24
+Description: hilo roto en inicio de buffer</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>GERSON ANDRE VIVANCO DIESTRA</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2026-09-13 09:52:26</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>2026-09-13 09:52:51</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>2026-09-13 09:52:53</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CM-20260912-00000224</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>INC-20260912-00006175</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-09-12 16:23:51</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>running</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-09-08 23:51:12</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>235-ETH_LOS</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0135592</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0135592_LM_Ucayali_America</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>CORTE</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>16:17:28</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>unscheduled</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Edgar Soto</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2026-09-12 16:45:33</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CM-20260912-00000212</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>INC-20260912-00004906</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-09-12 13:42:51</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-12 18:22:05</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>235-ETH_LOS</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>0135774</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>0135774_LM_Lima_Centro</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>CORTE</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>17:33:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>unscheduled</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Edgar Soto</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2026-09-12 15:30:01</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CM-20260912-00000036</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>INC-20260912-00001099</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-09-12 03:53:39</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>772874247-The distribute fiber is broken or the OLT cannot receive expected optical signals from the ONT(LOSi LOBi)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0135588</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0135588_LM_Trenemann</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>CAIDA</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>08:02:56</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>05:07:02</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>unscheduled</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Edgar Soto</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2026-09-12 03:55:59</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CM-20260911-00000308</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>INC-20260911-00006754</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-09-11 19:31:09</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2507160001-ETH_LOS_CAIDA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0135588</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0135588_LM_Trenemann</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>CAIDA</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>13:11:05</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>unscheduled</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Edgar Soto</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2026-09-11 19:51:56</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CM-20260911-00000307</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>INC-20260911-00006754</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-09-11 19:31:09</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2507160006-ETH_LOS_Caida</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0135588</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0135588_LM_Trenemann</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>CAIDA</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>13:11:59</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>unscheduled</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Edgar Soto</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2026-09-11 19:51:02</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CM-20260911-00000271</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>INC-20260911-00005217</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-09-11 17:56:51</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-09-12 13:18:00</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-12 13:18:00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>10819-Hardware Fault</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0130238</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0130238_LM_Mello_Franco</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>ENTORNO_FALLA EQ/GESTION</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>15:03:10</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>JESUS MARIA</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Yoshua Quispe</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2026-09-11 17:59:51</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operator: user:Boris.Chivilchez
+Complete time: 2026-09-12 13:12:27
+Description: se hizo descartes en mufa principal, hilos ok </t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>GERSON ANDRE VIVANCO DIESTRA</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2026-09-12 13:12:29</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>2026-09-12 13:14:48</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>2026-09-12 13:14:50</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CM-20260911-00000266</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>INC-20260911-00006018</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-09-11 17:45:41</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:22:00</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:22:00</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>235-ETH_LOS</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>FO Cut</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0130387</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0130387_LM_Lurin</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>CORTE</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>15:14:27</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>LURIN</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Álvaro Ballarta</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2026-09-11 17:48:34</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Operator: user:bcastillod
+Complete time: 2026-09-13 11:18:58
+Description: NO Observación: SE llega a cordenadas brindadas por oym, se realiza revisión de mufa y se encuentra hilo roto al raz del buffer, hilo afectado es el nr 33 con dirección al cliente, se buscan hilos para realizar el cambio y se ubica hilo 30 que completa ruta sin atenuacion a siguiente mufa, se fusiona y se realiza el cambio de hilo entre mufa y mufa.</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>JUAN JOSE CARRION QUISPE</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:18:59</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:19:58</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:19:59</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CM-20260911-00000225</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>INC-20260911-00004937</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-09-11 15:20:10</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-11 15:30:25</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2505224-Optical Invalid</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0130135</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0130135_LM_Garcia_y_Garcia</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>ATENUADO</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>17:39:56</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>dispatched</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>Edgar Soto</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>2026-09-07 09:30:43</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2026-09-11 15:23:05</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
         <is>
           <t xml:space="preserve">Type: PAUSE
-Reason: Restricciones por temas de seguridad personal
-Operation time: 2026-09-07 18:10:27
-Creator: jhuayhuarima.cobra
-Description: Cámara a inspecciónar en vía con exceso transito vehicular </t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Operator: user:janastacio.cobra
+Reason: Restricciones de acceso por parte de terceros notificada a ENTEL
+Operation time: 2026-09-12 23:31:40
+Creator: vcauti.cobra
+Description: no hay acceso al edificio </t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operator: user:vcauti.cobra
 Complete time: 
 Description: 
 Operator: user:jhuayhuarima.cobra
 Complete time: 
 Description: 
-Operator: user:vcauti.cobra
+Operator: user:gvivanco.cobra
 Complete time: 
 Description: </t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
+      <c r="X22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>VICTOR WILLIAM CAUTI AGUIRRE</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>GERSON ANDRE VIVANCO DIESTRA</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH13" t="inlineStr">
+      <c r="AH22" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AI22" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CM-20260907-00000051</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>INC-20260907-00001641</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2026-09-07 07:00:26</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:58:00</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CM-20260911-00000224</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>INC-20260911-00004937</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-09-11 15:20:10</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-11 15:30:25</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2505224-Optical Invalid</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0130135</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0130135_LM_Garcia_y_Garcia</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>ATENUADO</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>17:40:22</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>unscheduled</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Edgar Soto</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2026-09-11 15:22:39</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CM-20260911-00000206</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>INC-20260911-00004258</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-09-11 14:27:49</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-09-12 18:14:06</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-09-07 07:58:51</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>772907009-The feeder fiber is broken or OLT can not receive any expected optical signals (LOS)</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-12 18:14:06</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2508200002-ETH_LOS_CAIDA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>prueba</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0130136</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0130136_LM_Bolivia</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
+      <c r="I24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0130238</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0130238_LM_Mello_Franco</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>CAIDA</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>10:24:27</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>BREÑA</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>18:33:00</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>JESUS MARIA</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>Yoshua Quispe</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>2026-09-07 07:09:12</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2026-09-11 14:30:01</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Operator: user:Boris.Chivilchez
-Complete time: 2026-09-07 13:54:57
-Description: Se tiene valores en naps</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Operator: user:Yuliza.Jaimes
+Complete time: 2026-09-12 17:50:26
+Description: prueba</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>JOHAN  HUAYHUARIMA LEON</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>ANDY JAVIER RODAS VILLAJUAN</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:55:02</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:55:28</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:55:33</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2026-09-12 17:50:28</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>2026-09-12 18:10:07</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>2026-09-12 18:10:12</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH14" t="inlineStr">
+      <c r="AH24" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
+      <c r="AI24" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CM-20260907-00000040</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>INC-20260907-00001335</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2026-09-07 05:45:08</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-09-07 15:50:00</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CM-20260911-00000204</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>INC-20260911-00004476</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-09-11 14:16:15</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>235-ETH_LOS</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>01348332</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>01348332_LM_MC_Jiron_Tarma</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>CORTE</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>18:43:49</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>unscheduled</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Edgar Soto</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2026-09-11 14:19:12</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CM-20260911-00000177</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>INC-20260911-00003913</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:01:37</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>235-ETH_LOS</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0130449</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0130449_LM_Pq_Ind_Lurin</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>CORTE</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>19:59:33</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>LURIN</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>unscheduled</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Álvaro Ballarta</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:03:28</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CM-20260911-00000137</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>INC-20260911-00003210</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:28:11</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-09-12 18:54:00</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-09-07 06:36:08</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2505274-Physical Port Down</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Rectifier</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>0130119</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0130119_LM_Estadio_Alianza</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-12 16:52:33</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2601500-ETH_LOS</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>FO Cut</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0135774</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0135774_LM_Lima_Centro</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>CORTE</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>11:28:11</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>LA VICTORIA</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>21:33:37</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Edwin Oscco</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>2026-09-07 06:05:28</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Edgar Soto</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:29:24</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Operator: user:Boris.Chivilchez
-Complete time: 2026-09-07 15:46:07
-Description: se hizo pruebas de potencia y traza, queda limpio de site a site</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Operator: user:gvivanco.cobra
+Complete time: 
+Description: 
+Operator: user:Yuliza.Jaimes
+Complete time: 2026-09-12 18:50:26
+Description: hilo roto a 7klm</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>GABRIEL STTEFFANO AQUIJE CORNEJO</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>GERSON ANDRE VIVANCO DIESTRA</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2026-09-07 15:46:09</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>2026-09-07 15:47:07</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>2026-09-07 15:47:09</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2026-09-12 18:50:28</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>2026-09-12 18:51:22</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>2026-09-12 18:51:24</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/scripts/WOs List PEXT.xlsx
+++ b/scripts/WOs List PEXT.xlsx
@@ -447,7 +447,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>11:34:28</t>
+          <t>13:04:31</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>13:01:32</t>
+          <t>14:31:35</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>13:53:31</t>
+          <t>15:23:34</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>17:15:03</t>
+          <t>18:45:06</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>18:35:29</t>
+          <t>20:05:32</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>23:20:15</t>
+          <t>00:50:18</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>23:26:28</t>
+          <t>00:56:31</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>09:41:44</t>
+          <t>11:11:47</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>12:41:07</t>
+          <t>14:11:10</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>12:42:28</t>
+          <t>14:12:31</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>14:14:40</t>
+          <t>15:44:43</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>14:38:03</t>
+          <t>16:08:06</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>15:27:36</t>
+          <t>16:57:39</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>16:17:28</t>
+          <t>17:47:31</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>17:33:00</t>
+          <t>19:03:03</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>05:07:02</t>
+          <t>06:37:05</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>13:11:05</t>
+          <t>14:41:08</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>13:11:59</t>
+          <t>14:42:02</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>15:03:10</t>
+          <t>16:33:13</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>15:14:27</t>
+          <t>16:44:30</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>17:39:56</t>
+          <t>19:09:59</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>17:40:22</t>
+          <t>19:10:25</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>18:33:00</t>
+          <t>20:03:03</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>18:43:49</t>
+          <t>20:13:52</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>19:59:33</t>
+          <t>21:29:36</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>21:33:37</t>
+          <t>23:03:40</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">

--- a/scripts/WOs List PEXT.xlsx
+++ b/scripts/WOs List PEXT.xlsx
@@ -157,7 +157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AI27"/>
+  <dimension ref="A1:AI28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="24" max="24" width="26.0" customWidth="true"/>
@@ -377,17 +377,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CM-20260913-00000295</t>
+          <t>CM-20260914-00000121</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INC-20260913-00006712</t>
+          <t>INC-20260914-00003451</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-13 21:27:17</t>
+          <t>2026-09-14 12:58:04</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -422,12 +422,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0135587</t>
+          <t>0130449</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0135587_LM_Monserrate</t>
+          <t>0130449_LM_Pq_Ind_Lurin</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -447,7 +447,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>13:04:31</t>
+          <t>00:02:15</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>LURIN</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -472,12 +472,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Edgar Soto</t>
+          <t>Álvaro Ballarta</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-13 21:28:33</t>
+          <t>2026-09-14 13:00:52</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -542,49 +542,49 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CM-20260913-00000278</t>
+          <t>CM-20260914-00000090</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INC-20260913-00006137</t>
+          <t>INC-20260914-00002700</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-13 19:46:08</t>
+          <t>2026-09-14 11:04:23</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-13 20:39:25</t>
+          <t/>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>running</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-13 19:57:23</t>
+          <t/>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>235-ETH_LOS</t>
+          <t>12793-ETH_LINK_DOWN</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0130119</t>
+          <t>0134658</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0130119_LM_Estadio_Alianza</t>
+          <t>0134658_AQ_El_Chaparral</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -624,37 +624,37 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>14:31:35</t>
+          <t>01:56:51</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>LA VICTORIA</t>
+          <t>YURA</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>unscheduled</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Edwin Oscco</t>
+          <t>Ivan Bueno</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-13 20:01:29</t>
+          <t>2026-09-14 11:06:16</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-09-13 20:39:25</t>
+          <t/>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -719,525 +719,525 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t/>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>CM-20260913-00000295</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>INC-20260913-00006712</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-09-13 21:27:17</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>235-ETH_LOS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0135587</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0135587_LM_Monserrate</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>CORTE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>15:34:34</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>unscheduled</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Edgar Soto</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-09-13 21:28:33</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CM-20260913-00000278</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>INC-20260913-00006137</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-09-13 19:46:08</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-09-13 20:39:25</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>cancel</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-13 19:57:23</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>235-ETH_LOS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0130119</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0130119_LM_Estadio_Alianza</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>CORTE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>17:01:38</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>LA VICTORIA</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>canceled</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Edwin Oscco</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-09-13 20:01:29</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>2026-09-13 20:39:25</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>CM-20260913-00000265</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>INC-20260913-00004502</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>2026-09-13 19:07:32</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>2026-09-14 07:00:00</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-09-14 07:00:00</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>235-ETH_LOS</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>prueba</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>0130387</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>0130387_LM_Lurin</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>CORTE</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>15:23:34</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>17:53:37</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>LURIN</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Álvaro Ballarta</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>2026-09-13 19:09:30</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Operator: user:bcastillod
 Complete time: 2026-09-14 06:57:02
 Description: hilo partido, en mufa</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>ANDY JAVIER RODAS VILLAJUAN</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>2026-09-14 06:57:03</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>2026-09-14 06:57:41</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2026-09-14 06:57:43</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CM-20260913-00000226</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>INC-20260913-00004824</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-09-13 15:46:30</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>235-ETH_LOS</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>013253025</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>013253025_LM_PS_UniversidadTecLimaSur</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>CORTE</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>18:45:06</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>inprocess</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Álvaro Ballarta</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>2026-09-13 15:47:58</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>depart</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>JHONATAN VICENTE ANASTACIO SAIRUTUPAC</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CM-20260913-00000204</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>INC-20260913-00004410</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-09-13 14:26:48</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>235-ETH_LOS</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0136114</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0136114_LM_Jesus_Redentor</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>CORTE</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>20:05:32</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>SAN MIGUEL</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>dispatched</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Yoshua Quispe</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>2026-09-13 14:27:32</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>dispatch</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>GERSON ANDRE VIVANCO DIESTRA</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1264,115 +1264,471 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>CM-20260913-00000226</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>INC-20260913-00004824</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-09-13 15:46:30</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>235-ETH_LOS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>013253025</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>013253025_LM_PS_UniversidadTecLimaSur</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>CORTE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>21:15:09</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>inprocess</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Álvaro Ballarta</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-09-13 15:47:58</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>arrive</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>JHONATAN VICENTE ANASTACIO SAIRUTUPAC</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CM-20260913-00000204</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>INC-20260913-00004410</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-09-13 14:26:48</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-09-14 11:42:00</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-14 11:42:00</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>235-ETH_LOS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>FO Cut</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0136114</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0136114_LM_Jesus_Redentor</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>CORTE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>22:35:35</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>SAN MIGUEL</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Yoshua Quispe</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-09-13 14:27:32</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operator: user:Yuliza.Jaimes
+Complete time: 2026-09-14 11:37:33
+Description: hilo cortado </t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>GERSON ANDRE VIVANCO DIESTRA</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-09-14 11:37:35</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2026-09-14 11:38:53</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2026-09-14 11:38:55</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>CM-20260913-00000111</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>INC-20260912-00007617</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>2026-09-12 20:18:11</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>2026-09-13 11:18:04</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>2026-09-13 10:31:04</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>235-ETH_LOS</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>FO Cut</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>0130015</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>0130015_LM_Huayucari</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>CORTE</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>00:50:18</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>03:20:21</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>ATE</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Martín Figueroa</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>2026-09-13 09:42:46</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Operator: user:Yuliza.Jaimes
 Complete time: 2026-09-13 11:14:12
@@ -1380,179 +1736,179 @@
 solución se realizo cambio de cuenta entre mufas en tramo</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
+      <c r="X9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>JUAN JOSE CARRION QUISPE</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>2026-09-13 11:14:14</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>2026-09-13 11:14:58</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2026-09-13 11:14:59</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AH9" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>CM-20260913-00000107</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>INC-20260913-00002313</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>2026-09-13 09:35:53</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>2026-09-14 01:22:01</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>2026-09-13 19:56:29</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>2601500-ETH_LOS</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>FO Cut</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>0130015</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>0130015_LM_Huayucari</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>CORTE</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>00:56:31</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>03:26:34</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>ATE</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Martín Figueroa</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>2026-09-13 09:36:33</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t xml:space="preserve">Operator: user:Jpachecom.cobra
 Complete time: 
@@ -1566,174 +1922,174 @@
 solución: tendido de fibra y creación de dos bandejas de averia  se deja con señal ok tendido de 100 metros </t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="X10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>JUAN JOSE CARRION QUISPE</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>2026-09-14 01:18:55</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>2026-09-14 01:20:00</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2026-09-14 01:20:03</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AH10" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>CM-20260912-00000296</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>INC-20260912-00008409</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>2026-09-12 23:13:30</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>2601500-ETH_LOS</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>0130176</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>0130176_LM_Huanuco</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>CORTE</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>11:11:47</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>13:41:50</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>LA VICTORIA</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>inprocess</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Edwin Oscco</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>2026-09-12 23:21:17</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t xml:space="preserve">Type: PAUSE
 Reason: Restricciones por temas de seguridad personal
@@ -1747,896 +2103,896 @@
 Description: Se reanuda labores </t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t xml:space="preserve">Operator: user:rmercado.cobra
 Complete time: 
 Description: </t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
+      <c r="X11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>depart</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>arrive</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
         <is>
           <t>RUBEN HILDO MERCADO CAMARGO</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AH11" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CM-20260912-00000266</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>INC-20260912-00007617</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-09-12 20:18:11</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-09-13 11:18:04</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-09-13 10:31:04</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>235-ETH_LOS</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0162762</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0162762_LM_HB_Ate_AMT</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>CORTE</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>14:11:10</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>ATE</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>canceled</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Martin Figueroa</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2026-09-12 20:21:54</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>2026-09-13 09:41:28</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CM-20260912-00000265</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>INC-20260912-00007617</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2026-09-12 20:18:11</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-09-13 11:18:04</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-09-13 10:31:04</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>235-ETH_LOS</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0162762</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0162762_LM_HB_Ate_AMT</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>CORTE</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>14:12:31</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>ATE</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>canceled</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Martin Figueroa</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2026-09-12 20:20:33</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>2026-09-13 09:41:54</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>CM-20260912-00000266</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>INC-20260912-00007617</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-09-12 20:18:11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:18:04</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-13 10:31:04</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>235-ETH_LOS</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0162762</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0162762_LM_HB_Ate_AMT</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>CORTE</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>16:41:13</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>canceled</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Martin Figueroa</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2026-09-12 20:21:54</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>2026-09-13 09:41:28</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CM-20260912-00000265</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>INC-20260912-00007617</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-09-12 20:18:11</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:18:04</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-13 10:31:04</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>235-ETH_LOS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0162762</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0162762_LM_HB_Ate_AMT</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>CORTE</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>16:42:34</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>canceled</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Martin Figueroa</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2026-09-12 20:20:33</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>2026-09-13 09:41:54</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>CM-20260912-00000244</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>INC-20260912-00006953</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>2026-09-12 18:37:56</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>2026-09-13 09:40:00</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>2026-09-13 09:29:47</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>235-ETH_LOS</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>FO Cut</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>0130522</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0130522_LM_IB_MSO_San_Borja</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>P0+</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>CORTE</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>15:44:43</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>18:14:46</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>SAN BORJA</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Álvaro Ballarta</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jesus Susano</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
         <is>
           <t>2026-09-12 18:48:21</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t xml:space="preserve">Operator: user:Boris.Chivilchez
 Complete time: 2026-09-13 09:31:17
 Description: se empalma hilo </t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
+      <c r="X14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>VICTOR WILLIAM CAUTI AGUIRRE</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>2026-09-13 09:31:21</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>2026-09-13 09:37:50</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>2026-09-13 09:37:52</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AH14" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>CM-20260912-00000238</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>INC-20260912-00006860</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>2026-09-12 18:23:31</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>2026-09-12 18:47:01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>cancel</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>235-ETH_LOS</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>0130283</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>0130283_LM_Quechuas</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>CORTE</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>16:08:06</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>18:38:09</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>ATE</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>canceled</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Martín Figueroa</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>2026-09-12 18:24:58</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
+      <c r="X15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>create</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
         <is>
           <t>2026-09-12 18:47:01</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH13" t="inlineStr">
+      <c r="AH15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AI15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>CM-20260912-00000231</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>INC-20260912-00006553</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>2026-09-12 17:32:40</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>2026-09-13 09:56:00</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>2026-09-13 09:56:00</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>235-ETH_LOS</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>FO Cut</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>0130373</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>0130373_LM_Carabayllo</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>CORTE</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>16:57:39</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>19:27:42</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>PUENTE PIEDRA</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Edgar Soto</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>2026-09-12 17:35:25</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Operator: user:Jpachecom.cobra
 Complete time: 
@@ -2649,413 +3005,59 @@
 Description: hilo roto en inicio de buffer</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
+      <c r="X16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>GERSON ANDRE VIVANCO DIESTRA</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>2026-09-13 09:52:26</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>2026-09-13 09:52:51</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>2026-09-13 09:52:53</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH14" t="inlineStr">
+      <c r="AH16" t="inlineStr">
         <is>
           <t>Media</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CM-20260912-00000224</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>INC-20260912-00006175</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2026-09-12 16:23:51</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>235-ETH_LOS</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>0135592</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0135592_LM_Ucayali_America</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>CORTE</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>17:47:31</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>unscheduled</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Edgar Soto</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>2026-09-12 16:45:33</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CM-20260912-00000212</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>INC-20260912-00004906</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2026-09-12 13:42:51</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-09-12 18:22:05</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>235-ETH_LOS</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>0135774</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0135774_LM_Lima_Centro</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>CORTE</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>19:03:03</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>unscheduled</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Edgar Soto</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>2026-09-12 15:30:01</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Baja</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -3067,17 +3069,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CM-20260912-00000036</t>
+          <t>CM-20260912-00000224</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INC-20260912-00001099</t>
+          <t>INC-20260912-00006175</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-09-12 03:53:39</t>
+          <t>2026-09-12 16:23:51</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3097,7 +3099,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>772874247-The distribute fiber is broken or the OLT cannot receive expected optical signals from the ONT(LOSi LOBi)</t>
+          <t>235-ETH_LOS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3112,12 +3114,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0135588</t>
+          <t>0135592</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0135588_LM_Trenemann</t>
+          <t>0135592_LM_Ucayali_America</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -3127,17 +3129,17 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>CAIDA</t>
+          <t>CORTE</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>06:37:05</t>
+          <t>20:17:34</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -3167,7 +3169,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2026-09-12 03:55:59</t>
+          <t>2026-09-12 16:45:33</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -3244,17 +3246,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CM-20260911-00000308</t>
+          <t>CM-20260912-00000212</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>INC-20260911-00006754</t>
+          <t>INC-20260912-00004906</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-11 19:31:09</t>
+          <t>2026-09-12 13:42:51</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3269,12 +3271,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-12 18:22:05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2507160001-ETH_LOS_CAIDA</t>
+          <t>235-ETH_LOS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3289,32 +3291,32 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0135588</t>
+          <t>0135774</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0135588_LM_Trenemann</t>
+          <t>0135774_LM_Lima_Centro</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>CAIDA</t>
+          <t>CORTE</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>14:41:08</t>
+          <t>21:33:06</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -3344,7 +3346,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2026-09-11 19:51:56</t>
+          <t>2026-09-12 15:30:01</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -3409,7 +3411,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
@@ -3421,17 +3423,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CM-20260911-00000307</t>
+          <t>CM-20260912-00000036</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>INC-20260911-00006754</t>
+          <t>INC-20260912-00001099</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-09-11 19:31:09</t>
+          <t>2026-09-12 03:53:39</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3451,7 +3453,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2507160006-ETH_LOS_Caida</t>
+          <t>772874247-The distribute fiber is broken or the OLT cannot receive expected optical signals from the ONT(LOSi LOBi)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3491,7 +3493,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>14:42:02</t>
+          <t>09:07:08</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3521,7 +3523,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2026-09-11 19:51:02</t>
+          <t>2026-09-12 03:55:59</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -3598,468 +3600,822 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>CM-20260911-00000308</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>INC-20260911-00006754</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-09-11 19:31:09</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2507160001-ETH_LOS_CAIDA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0135588</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0135588_LM_Trenemann</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>CAIDA</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>17:11:11</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>unscheduled</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Edgar Soto</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2026-09-11 19:51:56</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CM-20260911-00000307</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>INC-20260911-00006754</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-09-11 19:31:09</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2507160006-ETH_LOS_Caida</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0135588</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0135588_LM_Trenemann</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>CAIDA</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>17:12:05</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>unscheduled</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Edgar Soto</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2026-09-11 19:51:02</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>CM-20260911-00000271</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>INC-20260911-00005217</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>2026-09-11 17:56:51</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>2026-09-12 13:18:00</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>2026-09-12 13:18:00</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>10819-Hardware Fault</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>0130238</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>0130238_LM_Mello_Franco</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>ENTORNO_FALLA EQ/GESTION</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>16:33:13</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>19:03:16</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>JESUS MARIA</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>Yoshua Quispe</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>2026-09-11 17:59:51</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t xml:space="preserve">Operator: user:Boris.Chivilchez
 Complete time: 2026-09-12 13:12:27
 Description: se hizo descartes en mufa principal, hilos ok </t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
+      <c r="X22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>GERSON ANDRE VIVANCO DIESTRA</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>2026-09-12 13:12:29</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>2026-09-12 13:14:48</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>2026-09-12 13:14:50</t>
         </is>
       </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH20" t="inlineStr">
+      <c r="AH22" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
+      <c r="AI22" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>CM-20260911-00000266</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>INC-20260911-00006018</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>2026-09-11 17:45:41</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>2026-09-13 11:22:00</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>2026-09-13 11:22:00</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>235-ETH_LOS</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>FO Cut</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>0130387</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>0130387_LM_Lurin</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>CORTE</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>16:44:30</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>19:14:33</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>LURIN</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>Álvaro Ballarta</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>2026-09-11 17:48:34</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>Operator: user:bcastillod
 Complete time: 2026-09-13 11:18:58
 Description: NO Observación: SE llega a cordenadas brindadas por oym, se realiza revisión de mufa y se encuentra hilo roto al raz del buffer, hilo afectado es el nr 33 con dirección al cliente, se buscan hilos para realizar el cambio y se ubica hilo 30 que completa ruta sin atenuacion a siguiente mufa, se fusiona y se realiza el cambio de hilo entre mufa y mufa.</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
+      <c r="X23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>JUAN JOSE CARRION QUISPE</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>2026-09-13 11:18:59</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>2026-09-13 11:19:58</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>2026-09-13 11:19:59</t>
         </is>
       </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH21" t="inlineStr">
+      <c r="AH23" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
+      <c r="AI23" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>CM-20260911-00000225</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>INC-20260911-00004937</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>2026-09-11 15:20:10</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>2026-09-11 15:30:25</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>2505224-Optical Invalid</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>0130135</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>0130135_LM_Garcia_y_Garcia</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>ATENUADO</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>19:09:59</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>21:40:02</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>dispatched</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>Edgar Soto</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>2026-09-11 15:23:05</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t xml:space="preserve">Type: PAUSE
 Reason: Restricciones de acceso por parte de terceros notificada a ENTEL
@@ -4068,7 +4424,7 @@
 Description: no hay acceso al edificio </t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t xml:space="preserve">Operator: user:vcauti.cobra
 Complete time: 
@@ -4081,769 +4437,415 @@
 Description: </t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
+      <c r="X24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>GERSON ANDRE VIVANCO DIESTRA</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH22" t="inlineStr">
+      <c r="AH24" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
+      <c r="AI24" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>CM-20260911-00000224</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>INC-20260911-00004937</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>2026-09-11 15:20:10</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>2026-09-11 15:30:25</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>2505224-Optical Invalid</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>0130135</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>0130135_LM_Garcia_y_Garcia</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>ATENUADO</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>19:10:25</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>21:40:28</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>unscheduled</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>Edgar Soto</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>2026-09-11 15:22:39</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
+      <c r="X25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>create</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH23" t="inlineStr">
+      <c r="AH25" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
+      <c r="AI25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>CM-20260911-00000206</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>INC-20260911-00004258</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>2026-09-11 14:27:49</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>2026-09-12 18:14:06</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>2026-09-12 18:14:06</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>2508200002-ETH_LOS_CAIDA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>prueba</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>0130238</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>0130238_LM_Mello_Franco</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>CAIDA</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>20:03:03</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>22:33:06</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>JESUS MARIA</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>Yoshua Quispe</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>2026-09-11 14:30:01</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>Operator: user:Yuliza.Jaimes
 Complete time: 2026-09-12 17:50:26
 Description: prueba</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
+      <c r="X26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>ANDY JAVIER RODAS VILLAJUAN</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>2026-09-12 17:50:28</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>2026-09-12 18:10:07</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>2026-09-12 18:10:12</t>
         </is>
       </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH24" t="inlineStr">
+      <c r="AH26" t="inlineStr">
         <is>
           <t>Media</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>CM-20260911-00000204</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>INC-20260911-00004476</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2026-09-11 14:16:15</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>235-ETH_LOS</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>01348332</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>01348332_LM_MC_Jiron_Tarma</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>CORTE</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>20:13:52</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>unscheduled</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Edgar Soto</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>2026-09-11 14:19:12</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>CM-20260911-00000177</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>INC-20260911-00003913</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2026-09-11 13:01:37</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>235-ETH_LOS</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>0130449</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0130449_LM_Pq_Ind_Lurin</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>CORTE</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>21:29:36</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>LURIN</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>unscheduled</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Álvaro Ballarta</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>2026-09-11 13:03:28</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Alta</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
@@ -4855,62 +4857,62 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CM-20260911-00000137</t>
+          <t>CM-20260911-00000204</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>INC-20260911-00003210</t>
+          <t>INC-20260911-00004476</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-09-11 11:28:11</t>
+          <t>2026-09-11 14:16:15</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-12 18:54:00</t>
+          <t/>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>running</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-12 16:52:33</t>
+          <t/>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2601500-ETH_LOS</t>
+          <t>235-ETH_LOS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>FO Cut</t>
+          <t/>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t/>
+          <t>Total</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0135774</t>
+          <t>01348332</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0135774_LM_Lima_Centro</t>
+          <t>01348332_LM_MC_Jiron_Tarma</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -4925,7 +4927,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>23:03:40</t>
+          <t>22:43:55</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4945,7 +4947,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>unscheduled</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -4955,7 +4957,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2026-09-11 11:29:24</t>
+          <t>2026-09-11 14:19:12</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -4965,12 +4967,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Operator: user:gvivanco.cobra
-Complete time: 
-Description: 
-Operator: user:Yuliza.Jaimes
-Complete time: 2026-09-12 18:50:26
-Description: hilo roto a 7klm</t>
+          <t>'-</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -4985,12 +4982,12 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>close</t>
+          <t>create</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>GERSON ANDRE VIVANCO DIESTRA</t>
+          <t/>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -5000,17 +4997,17 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-09-12 18:50:28</t>
+          <t/>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>2026-09-12 18:51:22</t>
+          <t/>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2026-09-12 18:51:24</t>
+          <t/>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -5025,10 +5022,187 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CM-20260911-00000177</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>INC-20260911-00003913</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:01:37</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>235-ETH_LOS</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0130449</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0130449_LM_Pq_Ind_Lurin</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>CORTE</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>23:59:39</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>LURIN</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>unscheduled</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Álvaro Ballarta</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:03:28</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/scripts/WOs List PEXT.xlsx
+++ b/scripts/WOs List PEXT.xlsx
@@ -157,7 +157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AI28"/>
+  <dimension ref="A1:AI27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="24" max="24" width="26.0" customWidth="true"/>
@@ -447,7 +447,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>00:02:15</t>
+          <t>01:02:17</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>01:56:51</t>
+          <t>02:56:53</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14 13:18:30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>15:34:34</t>
+          <t>16:34:36</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>17:01:38</t>
+          <t>18:01:40</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>17:53:37</t>
+          <t>18:53:39</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>21:15:09</t>
+          <t>22:15:11</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>22:35:35</t>
+          <t>23:35:37</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>03:20:21</t>
+          <t>04:20:23</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>03:26:34</t>
+          <t>04:26:36</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>13:41:50</t>
+          <t>14:41:52</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>16:41:13</t>
+          <t>17:41:15</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>16:42:34</t>
+          <t>17:42:36</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>18:14:46</t>
+          <t>19:14:48</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>18:38:09</t>
+          <t>19:38:11</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>19:27:42</t>
+          <t>20:27:44</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>20:17:34</t>
+          <t>21:17:36</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>21:33:06</t>
+          <t>22:33:08</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>09:07:08</t>
+          <t>10:07:10</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>17:11:11</t>
+          <t>18:11:13</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>17:12:05</t>
+          <t>18:12:07</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>19:03:16</t>
+          <t>20:03:18</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>19:14:33</t>
+          <t>20:14:35</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>21:40:02</t>
+          <t>22:40:04</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>21:40:28</t>
+          <t>22:40:30</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>22:33:06</t>
+          <t>23:33:08</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>22:43:55</t>
+          <t>23:43:57</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -5026,183 +5026,6 @@
         </is>
       </c>
       <c r="AI27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>CM-20260911-00000177</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>INC-20260911-00003913</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2026-09-11 13:01:37</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>235-ETH_LOS</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>0130449</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0130449_LM_Pq_Ind_Lurin</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>CORTE</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>23:59:39</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>LURIN</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>unscheduled</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Álvaro Ballarta</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>2026-09-11 13:03:28</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/scripts/WOs List PEXT.xlsx
+++ b/scripts/WOs List PEXT.xlsx
@@ -157,7 +157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AI27"/>
+  <dimension ref="A1:AI25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="24" max="24" width="26.0" customWidth="true"/>
@@ -447,7 +447,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>01:02:17</t>
+          <t>01:32:11</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>02:56:53</t>
+          <t>03:26:47</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>16:34:36</t>
+          <t>17:04:30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>18:01:40</t>
+          <t>18:31:34</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>18:53:39</t>
+          <t>19:23:33</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1279,17 +1279,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14 14:22:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14 14:22:00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t/>
+          <t>FO Cut</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>22:15:11</t>
+          <t>22:45:05</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>inprocess</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1374,7 +1374,9 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t>Operator: user:Boris.Chivilchez
+Complete time: 2026-09-14 14:17:43
+Description: HILO QUEBRADO EN MUFA POR MANIPULACIÓN DE TERCERO</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1389,7 +1391,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>arrive</t>
+          <t>close</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1404,17 +1406,17 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14 14:17:45</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14 14:18:54</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14 14:18:57</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1506,12 +1508,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>23:35:37</t>
+          <t>00:05:31</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1690,7 +1692,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>04:20:23</t>
+          <t>04:50:17</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1870,7 +1872,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>04:26:36</t>
+          <t>04:56:30</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2056,7 +2058,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>14:41:52</t>
+          <t>15:11:46</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2244,7 +2246,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>17:41:15</t>
+          <t>18:11:09</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2421,7 +2423,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>17:42:36</t>
+          <t>18:12:30</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2598,7 +2600,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>19:14:48</t>
+          <t>19:44:42</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2777,7 +2779,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>19:38:11</t>
+          <t>20:08:05</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2954,7 +2956,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>20:27:44</t>
+          <t>20:57:38</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -3139,7 +3141,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>21:17:36</t>
+          <t>21:47:30</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -3316,7 +3318,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>22:33:08</t>
+          <t>23:03:02</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -3493,7 +3495,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>10:07:10</t>
+          <t>10:37:04</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3670,7 +3672,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>18:11:13</t>
+          <t>18:41:07</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3847,7 +3849,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>18:12:07</t>
+          <t>18:42:01</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -4024,7 +4026,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>20:03:18</t>
+          <t>20:33:12</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -4203,7 +4205,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>20:14:35</t>
+          <t>20:44:29</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -4382,7 +4384,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>22:40:04</t>
+          <t>23:09:58</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -4571,7 +4573,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>22:40:30</t>
+          <t>23:10:24</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -4672,362 +4674,6 @@
       <c r="AI25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>CM-20260911-00000206</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>INC-20260911-00004258</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2026-09-11 14:27:49</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-09-12 18:14:06</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-09-12 18:14:06</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2508200002-ETH_LOS_CAIDA</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>prueba</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>0130238</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0130238_LM_Mello_Franco</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>CAIDA</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>23:33:08</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>JESUS MARIA</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Yoshua Quispe</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>2026-09-11 14:30:01</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Operator: user:Yuliza.Jaimes
-Complete time: 2026-09-12 17:50:26
-Description: prueba</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>close</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>ANDY JAVIER RODAS VILLAJUAN</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2026-09-12 17:50:28</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>2026-09-12 18:10:07</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>2026-09-12 18:10:12</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>CM-20260911-00000204</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>INC-20260911-00004476</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2026-09-11 14:16:15</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>235-ETH_LOS</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>01348332</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>01348332_LM_MC_Jiron_Tarma</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>CORTE</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>23:43:57</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>unscheduled</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Edgar Soto</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>2026-09-11 14:19:12</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
     </row>

--- a/scripts/WOs List PEXT.xlsx
+++ b/scripts/WOs List PEXT.xlsx
@@ -157,7 +157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AI25"/>
+  <dimension ref="A1:AI23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="24" max="24" width="26.0" customWidth="true"/>
@@ -447,7 +447,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>01:32:11</t>
+          <t>02:32:12</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>03:26:47</t>
+          <t>04:26:48</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>17:04:30</t>
+          <t>18:04:31</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>18:31:34</t>
+          <t>19:31:35</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>19:23:33</t>
+          <t>20:23:34</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>22:45:05</t>
+          <t>23:45:06</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>00:05:31</t>
+          <t>01:05:32</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>04:50:17</t>
+          <t>05:50:18</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>04:56:30</t>
+          <t>05:56:31</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>15:11:46</t>
+          <t>16:11:47</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>18:11:09</t>
+          <t>19:11:10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>18:12:30</t>
+          <t>19:12:31</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>19:44:42</t>
+          <t>20:44:43</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>20:08:05</t>
+          <t>21:08:06</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>20:57:38</t>
+          <t>21:57:39</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>21:47:30</t>
+          <t>22:47:31</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>23:03:02</t>
+          <t>00:03:03</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>10:37:04</t>
+          <t>11:37:05</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>18:41:07</t>
+          <t>19:41:08</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>18:42:01</t>
+          <t>19:42:02</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>20:33:12</t>
+          <t>21:33:13</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>20:44:29</t>
+          <t>21:44:30</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -4308,372 +4308,6 @@
       <c r="AI23" t="inlineStr">
         <is>
           <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>CM-20260911-00000225</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>INC-20260911-00004937</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2026-09-11 15:20:10</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-09-11 15:30:25</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2505224-Optical Invalid</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>0130135</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0130135_LM_Garcia_y_Garcia</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>ATENUADO</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>23:09:58</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>dispatched</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Edgar Soto</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>2026-09-11 15:23:05</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Type: PAUSE
-Reason: Restricciones de acceso por parte de terceros notificada a ENTEL
-Operation time: 2026-09-12 23:31:40
-Creator: vcauti.cobra
-Description: no hay acceso al edificio </t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Operator: user:vcauti.cobra
-Complete time: 
-Description: 
-Operator: user:jhuayhuarima.cobra
-Complete time: 
-Description: 
-Operator: user:gvivanco.cobra
-Complete time: 
-Description: </t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>GERSON ANDRE VIVANCO DIESTRA</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>CM-20260911-00000224</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>INC-20260911-00004937</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2026-09-11 15:20:10</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-09-11 15:30:25</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2505224-Optical Invalid</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>0130135</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0130135_LM_Garcia_y_Garcia</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>ATENUADO</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>23:10:24</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>unscheduled</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Edgar Soto</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>2026-09-11 15:22:39</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>

--- a/scripts/WOs List PEXT.xlsx
+++ b/scripts/WOs List PEXT.xlsx
@@ -157,7 +157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AI23"/>
+  <dimension ref="A1:AI18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="24" max="24" width="26.0" customWidth="true"/>
@@ -377,17 +377,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CM-20260914-00000121</t>
+          <t>CM-20260916-00000080</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INC-20260914-00003451</t>
+          <t>INC-20260916-00002555</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-14 12:58:04</t>
+          <t>2026-09-16 09:09:37</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -402,12 +402,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-16 10:34:37</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>235-ETH_LOS</t>
+          <t>2505224-Optical Invalid</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -422,12 +422,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0130449</t>
+          <t>0130210</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0130449_LM_Pq_Ind_Lurin</t>
+          <t>0130210_LM_San_Gabriel</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -437,7 +437,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>CORTE</t>
+          <t>ATENUADO</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -447,7 +447,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>02:32:12</t>
+          <t>02:35:52</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -462,22 +462,22 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>LURIN</t>
+          <t>SAN ISIDRO</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>unscheduled</t>
+          <t>dispatched</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Álvaro Ballarta</t>
+          <t>Edwin Oscco</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:00:52</t>
+          <t>2026-09-16 09:12:23</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -502,12 +502,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>dispatch</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t/>
+          <t>LAZARO SIHUI LUNA</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -554,17 +554,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CM-20260914-00000090</t>
+          <t>CM-20260916-00000069</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INC-20260914-00002700</t>
+          <t>INC-20260916-00001814</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-14 11:04:23</t>
+          <t>2026-09-16 06:48:19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12793-ETH_LINK_DOWN</t>
+          <t>2601500-ETH_LOS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0134658</t>
+          <t>0130033</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0134658_AQ_El_Chaparral</t>
+          <t>0130033_LM_San_Juan_de_Mirafl</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -624,37 +624,37 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>04:26:48</t>
+          <t>04:54:52</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>YURA</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>unscheduled</t>
+          <t>dispatched</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Ivan Bueno</t>
+          <t>Álvaro Ballarta</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-14 11:06:16</t>
+          <t>2026-09-16 06:53:23</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -664,7 +664,9 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t xml:space="preserve">Operator: user:arodas.cobra
+Complete time: 
+Description: </t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -679,12 +681,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t/>
+          <t>ANDY JAVIER RODAS VILLAJUAN</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -719,29 +721,29 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CM-20260913-00000295</t>
+          <t>CM-20260916-00000006</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INC-20260913-00006712</t>
+          <t>INC-20260916-00000142</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-13 21:27:17</t>
+          <t>2026-09-16 00:25:18</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -756,7 +758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18:30</t>
+          <t/>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -776,12 +778,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0135587</t>
+          <t>0130209</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0135587_LM_Monserrate</t>
+          <t>0130209_LM_San_Marcos</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -801,7 +803,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>18:04:31</t>
+          <t>11:20:47</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -816,22 +818,22 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>unscheduled</t>
+          <t>inprocess</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Edgar Soto</t>
+          <t>Yoshua Quispe</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-13 21:28:33</t>
+          <t>2026-09-16 00:27:28</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -841,7 +843,9 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t xml:space="preserve">Operator: user:gaquije.cobra
+Complete time: 
+Description: </t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -856,12 +860,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>arrive</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t/>
+          <t>GABRIEL STTEFFANO AQUIJE CORNEJO</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -896,44 +900,44 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CM-20260913-00000278</t>
+          <t>CM-20260915-00000232</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INC-20260913-00006137</t>
+          <t>INC-20260915-00006028</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-13 19:46:08</t>
+          <t>2026-09-15 18:02:26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-13 20:39:25</t>
+          <t>2026-09-15 18:32:01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-13 19:57:23</t>
+          <t>2026-09-15 18:32:02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -953,12 +957,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0130119</t>
+          <t>0130012</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0130119_LM_Estadio_Alianza</t>
+          <t>0130012_LM_Pando</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -978,7 +982,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>19:31:35</t>
+          <t>17:37:25</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -993,22 +997,22 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>LA VICTORIA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Edwin Oscco</t>
+          <t>Edgar Soto</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-13 20:01:29</t>
+          <t>2026-09-15 18:10:50</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1018,7 +1022,9 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t>Operator: user:alexander.farfan
+Complete time: 2026-09-15 18:27:22
+Description: Todo ok</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1033,12 +1039,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>close</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t/>
+          <t>Alexander Farfan Terrones</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1048,22 +1054,22 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-15 18:27:23</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-15 18:28:42</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-15 18:28:44</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-09-13 20:39:25</t>
+          <t/>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1085,22 +1091,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CM-20260913-00000265</t>
+          <t>CM-20260915-00000219</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INC-20260913-00004502</t>
+          <t>INC-20260915-00005864</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-13 19:07:32</t>
+          <t>2026-09-15 17:21:56</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-14 07:00:00</t>
+          <t>2026-09-15 17:40:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1110,7 +1116,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-14 07:00:00</t>
+          <t>2026-09-15 17:38:55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1120,7 +1126,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>prueba</t>
+          <t/>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1155,7 +1161,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>20:23:34</t>
+          <t>18:21:09</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1185,7 +1191,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-13 19:09:30</t>
+          <t>2026-09-15 17:27:06</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1195,9 +1201,9 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Operator: user:bcastillod
-Complete time: 2026-09-14 06:57:02
-Description: hilo partido, en mufa</t>
+          <t xml:space="preserve">Operator: user:alexander.farfan
+Complete time: 2026-09-15 17:37:10
+Description: Finalizado </t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1217,7 +1223,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>ANDY JAVIER RODAS VILLAJUAN</t>
+          <t>Alexander Farfan Terrones</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1227,17 +1233,17 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-09-14 06:57:03</t>
+          <t>2026-09-15 17:37:12</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2026-09-14 06:57:41</t>
+          <t>2026-09-15 17:37:32</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-09-14 06:57:43</t>
+          <t>2026-09-15 17:37:34</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1252,7 +1258,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1264,22 +1270,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CM-20260913-00000226</t>
+          <t>CM-20260915-00000175</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INC-20260913-00004824</t>
+          <t>INC-20260915-00005047</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-13 15:46:30</t>
+          <t>2026-09-15 14:55:59</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-14 14:22:00</t>
+          <t>2026-09-16 07:02:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1289,12 +1295,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-14 14:22:00</t>
+          <t>2026-09-16 07:02:00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>235-ETH_LOS</t>
+          <t>1-R_LOS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1309,12 +1315,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>013253025</t>
+          <t>0135143</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>013253025_LM_PS_UniversidadTecLimaSur</t>
+          <t>0135143_LM_PS_Placido_Jimenez</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1334,7 +1340,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>23:45:06</t>
+          <t>20:48:36</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1349,7 +1355,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>VILLA EL SALVADOR</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1359,12 +1365,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Álvaro Ballarta</t>
+          <t>Edgar Soto</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-13 15:47:58</t>
+          <t>2026-09-15 14:59:39</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1374,9 +1380,9 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Operator: user:Boris.Chivilchez
-Complete time: 2026-09-14 14:17:43
-Description: HILO QUEBRADO EN MUFA POR MANIPULACIÓN DE TERCERO</t>
+          <t>Operator: user:Yuliza.Jaimes
+Complete time: 2026-09-16 06:57:16
+Description: se  pasa cable y coloca una mufa</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1396,7 +1402,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>JHONATAN VICENTE ANASTACIO SAIRUTUPAC</t>
+          <t>VICTOR WILLIAM CAUTI AGUIRRE</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1406,17 +1412,17 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:45</t>
+          <t>2026-09-16 06:57:18</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2026-09-14 14:18:54</t>
+          <t>2026-09-16 06:58:07</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2026-09-14 14:18:57</t>
+          <t>2026-09-16 06:58:10</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1426,7 +1432,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t/>
+          <t>No</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -1443,32 +1449,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CM-20260913-00000204</t>
+          <t>CM-20260915-00000113</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>INC-20260913-00004410</t>
+          <t>INC-20260915-00003533</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-13 14:26:48</t>
+          <t>2026-09-15 11:25:39</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-14 11:42:00</t>
+          <t>2026-09-15 13:26:32</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-14 11:42:00</t>
+          <t>2026-09-15 12:41:04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1478,27 +1484,27 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FO Cut</t>
+          <t/>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t/>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0136114</t>
+          <t>0130522</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0136114_LM_Jesus_Redentor</t>
+          <t>0130522_LM_IB_MSO_San_Borja</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P0+</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1513,7 +1519,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>01:05:32</t>
+          <t>00:10:44</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1528,22 +1534,22 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>SAN MIGUEL</t>
+          <t>SAN BORJA</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Yoshua Quispe</t>
+          <t>Jesus Susano</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-13 14:27:32</t>
+          <t>2026-09-15 11:37:31</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1553,9 +1559,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator: user:Yuliza.Jaimes
-Complete time: 2026-09-14 11:37:33
-Description: hilo cortado </t>
+          <t>'-</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1570,12 +1574,12 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>close</t>
+          <t>dispatch</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>GERSON ANDRE VIVANCO DIESTRA</t>
+          <t>GABRIEL STTEFFANO AQUIJE CORNEJO</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1585,22 +1589,22 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-09-14 11:37:35</t>
+          <t/>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2026-09-14 11:38:53</t>
+          <t/>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-09-14 11:38:55</t>
+          <t/>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-15 13:26:32</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1610,7 +1614,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -1622,22 +1626,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CM-20260913-00000111</t>
+          <t>CM-20260915-00000078</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>INC-20260912-00007617</t>
+          <t>INC-20260915-00002763</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-12 20:18:11</t>
+          <t>2026-09-15 09:49:26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-13 11:18:04</t>
+          <t>2026-09-15 19:20:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1647,7 +1651,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-13 10:31:04</t>
+          <t>2026-09-15 17:49:26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1667,17 +1671,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0130015</t>
+          <t>0130387</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0130015_LM_Huayucari</t>
+          <t>0130387_LM_Lurin</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1692,7 +1696,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>05:50:18</t>
+          <t>01:54:04</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1707,7 +1711,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>ATE</t>
+          <t>LURIN</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1717,12 +1721,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Martín Figueroa</t>
+          <t>Álvaro Ballarta</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-13 09:42:46</t>
+          <t>2026-09-15 09:54:11</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1732,10 +1736,9 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Operator: user:Yuliza.Jaimes
-Complete time: 2026-09-13 11:14:12
-Description: se encontro hilo averiado en tramo
-solución se realizo cambio de cuenta entre mufas en tramo</t>
+          <t xml:space="preserve">Operator: user:Yuliza.Jaimes
+Complete time: 2026-09-15 19:16:08
+Description: SE UBICA HILO QUEBRADO EN MUFA, SE EMPALMA Y SE DEJA SERVICIO OPERATIVO </t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1755,7 +1758,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>JUAN JOSE CARRION QUISPE</t>
+          <t>JHONATAN VICENTE ANASTACIO SAIRUTUPAC</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1765,17 +1768,17 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-09-13 11:14:14</t>
+          <t>2026-09-15 19:16:10</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2026-09-13 11:14:58</t>
+          <t>2026-09-15 19:17:00</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-09-13 11:14:59</t>
+          <t>2026-09-15 19:17:01</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1790,7 +1793,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -1802,22 +1805,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CM-20260913-00000107</t>
+          <t>CM-20260914-00000241</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>INC-20260913-00002313</t>
+          <t>INC-20260914-00006691</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-13 09:35:53</t>
+          <t>2026-09-14 22:32:31</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-14 01:22:01</t>
+          <t>2026-09-15 16:56:03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1827,12 +1830,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-13 19:56:29</t>
+          <t>2026-09-15 16:56:03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2601500-ETH_LOS</t>
+          <t>235-ETH_LOS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1847,12 +1850,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0130015</t>
+          <t>0135588</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0130015_LM_Huayucari</t>
+          <t>0135588_LM_Trenemann</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1872,7 +1875,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>05:56:31</t>
+          <t>13:12:51</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1887,7 +1890,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>ATE</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1897,12 +1900,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Martín Figueroa</t>
+          <t>Edgar Soto</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-09-13 09:36:33</t>
+          <t>2026-09-14 22:35:24</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1912,259 +1915,254 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator: user:Jpachecom.cobra
+          <t xml:space="preserve">Operator: user:Boris.Chivilchez
+Complete time: 2026-09-15 16:52:16
+Description: se encuentra hilo roto a 135 metros </t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>GERSON ANDRE VIVANCO DIESTRA</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:52:17</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:53:12</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:53:14</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CM-20260914-00000222</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>INC-20260914-00005767</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-09-14 20:37:06</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-09-16 01:02:20</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-16 01:02:20</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>235-ETH_LOS</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>prueba</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0130387</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0130387_LM_Lurin</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>CORTE</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>15:10:22</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>LURIN</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Álvaro Ballarta</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2026-09-14 20:37:53</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Operator: user:vcauti.cobra
 Complete time: 
 Description: 
 Operator: user:jcarrion.cobra
 Complete time: 
 Description: 
-Operator: user:System
-Complete time: 2026-09-14 01:18:50
-Description: causa : ruptura de fibra por camión de gran altura 
-solución: tendido de fibra y creación de dos bandejas de averia  se deja con señal ok tendido de 100 metros </t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
+Operator: user:gustavo.yalle
+Complete time: 2026-09-16 00:57:25
+Description: SE REALIZA MEDICIONES DESDE EL
+SITE HACIA EL CLIENTE TELXIUS
+SE ENCUENTRA ATENUACIONES EN TRAMO SE PROCEDE A DEPURAR LOS EVENTOS
+SE LIBERAN HILOS EN MUFAS Y VUELVEN A
+EMPALMAR
+O&amp;M VALIDA SERVICIO (GUSTABO YALLE</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>JUAN JOSE CARRION QUISPE</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-09-14 01:18:55</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>2026-09-14 01:20:00</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2026-09-14 01:20:03</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:57:27</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:58:42</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:58:44</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CM-20260912-00000296</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>INC-20260912-00008409</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2026-09-12 23:13:30</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2601500-ETH_LOS</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0130176</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0130176_LM_Huanuco</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>CORTE</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>16:11:47</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>LA VICTORIA</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>inprocess</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Edwin Oscco</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2026-09-12 23:21:17</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Type: PAUSE
-Reason: Restricciones por temas de seguridad personal
-Operation time: 2026-09-13 16:31:06
-Creator: vcauti.cobra
-Description: por accesos y zona peligrosa
-Type: RESUME
-Reason: 
-Operation time: 2026-09-14 08:39:41
-Creator: rmercado.cobra
-Description: Se reanuda labores </t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Operator: user:rmercado.cobra
-Complete time: 
-Description: </t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>arrive</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>RUBEN HILDO MERCADO CAMARGO</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2176,22 +2174,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CM-20260912-00000266</t>
+          <t>CM-20260914-00000121</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INC-20260912-00007617</t>
+          <t>INC-20260914-00003451</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-12 20:18:11</t>
+          <t>2026-09-14 12:58:04</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-13 11:18:04</t>
+          <t>2026-09-15 07:04:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2201,7 +2199,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-13 10:31:04</t>
+          <t>2026-09-15 06:25:09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2211,22 +2209,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t/>
+          <t>FO Cut</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t/>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0162762</t>
+          <t>0130449</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0162762_LM_HB_Ate_AMT</t>
+          <t>0130449_LM_Pq_Ind_Lurin</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2246,7 +2244,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>19:11:10</t>
+          <t>22:47:23</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2261,22 +2259,22 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>ATE</t>
+          <t>LURIN</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Martin Figueroa</t>
+          <t>Álvaro Ballarta</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-09-12 20:21:54</t>
+          <t>2026-09-14 13:00:52</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2286,7 +2284,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t>Operator: user:vcauti.cobra
+Complete time: 
+Description: 
+Operator: user:Yuliza.Jaimes
+Complete time: 2026-09-15 06:59:58
+Description: se fusiona hilo</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -2301,12 +2304,12 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>close</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t/>
+          <t>VICTOR WILLIAM CAUTI AGUIRRE</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2316,27 +2319,27 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-15 06:59:59</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-15 07:00:24</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-15 07:00:26</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-09-13 09:41:28</t>
+          <t/>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -2353,22 +2356,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CM-20260912-00000265</t>
+          <t>CM-20260914-00000090</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INC-20260912-00007617</t>
+          <t>INC-20260914-00002700</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-12 20:18:11</t>
+          <t>2026-09-14 11:04:23</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-13 11:18:04</t>
+          <t>2026-09-15 12:56:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2378,17 +2381,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-13 10:31:04</t>
+          <t>2026-09-15 12:13:33</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>235-ETH_LOS</t>
+          <t>12793-ETH_LINK_DOWN</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t/>
+          <t>FO Cut</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2398,12 +2401,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0162762</t>
+          <t>0134658</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0162762_LM_HB_Ate_AMT</t>
+          <t>0134658_AQ_El_Chaparral</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2418,42 +2421,42 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>19:12:31</t>
+          <t>00:41:59</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>ATE</t>
+          <t>YURA</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Martin Figueroa</t>
+          <t>Ivan Bueno</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-09-12 20:20:33</t>
+          <t>2026-09-14 11:06:16</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -2463,7 +2466,9 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t>Operator: user:System
+Complete time: 2026-09-15 12:52:34
+Description: se empalma hilos en mufa</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -2478,12 +2483,12 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>close</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t/>
+          <t>GUSTAVO ALONSO CHUMBE VARGAS</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2493,27 +2498,27 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-15 12:52:35</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-15 12:53:14</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-15 12:53:15</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-09-13 09:41:54</t>
+          <t/>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -2523,39 +2528,39 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CM-20260912-00000244</t>
+          <t>CM-20260913-00000295</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INC-20260912-00006953</t>
+          <t>INC-20260913-00006712</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-12 18:37:56</t>
+          <t>2026-09-13 21:27:17</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-13 09:40:00</t>
+          <t/>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>running</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-13 09:29:47</t>
+          <t>2026-09-14 13:18:30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2565,27 +2570,27 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>FO Cut</t>
+          <t/>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t/>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0130522</t>
+          <t>0135587</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0130522_LM_IB_MSO_San_Borja</t>
+          <t>0135587_LM_Monserrate</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>P0+</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2595,12 +2600,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>20:44:43</t>
+          <t>14:19:42</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2615,22 +2620,22 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>SAN BORJA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>unscheduled</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Jesus Susano</t>
+          <t>Edgar Soto</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-09-12 18:48:21</t>
+          <t>2026-09-13 21:28:33</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2640,9 +2645,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator: user:Boris.Chivilchez
-Complete time: 2026-09-13 09:31:17
-Description: se empalma hilo </t>
+          <t>'-</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2657,12 +2660,12 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>close</t>
+          <t>create</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>VICTOR WILLIAM CAUTI AGUIRRE</t>
+          <t/>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2672,17 +2675,17 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-09-13 09:31:21</t>
+          <t/>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2026-09-13 09:37:50</t>
+          <t/>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2026-09-13 09:37:52</t>
+          <t/>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2697,34 +2700,34 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CM-20260912-00000238</t>
+          <t>CM-20260913-00000278</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INC-20260912-00006860</t>
+          <t>INC-20260913-00006137</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-12 18:23:31</t>
+          <t>2026-09-13 19:46:08</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-12 18:47:01</t>
+          <t>2026-09-13 20:39:25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2734,7 +2737,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-13 19:57:23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2754,17 +2757,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0130283</t>
+          <t>0130119</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0130283_LM_Quechuas</t>
+          <t>0130119_LM_Estadio_Alianza</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2774,12 +2777,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>21:08:06</t>
+          <t>15:46:46</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2794,7 +2797,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>ATE</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2804,12 +2807,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Martín Figueroa</t>
+          <t>Edwin Oscco</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-09-12 18:24:58</t>
+          <t>2026-09-13 20:01:29</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2864,7 +2867,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-09-12 18:47:01</t>
+          <t>2026-09-13 20:39:25</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2874,34 +2877,34 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CM-20260912-00000231</t>
+          <t>CM-20260913-00000265</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INC-20260912-00006553</t>
+          <t>INC-20260913-00004502</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-09-12 17:32:40</t>
+          <t>2026-09-13 19:07:32</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-13 09:56:00</t>
+          <t>2026-09-14 07:00:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2911,7 +2914,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-13 09:56:00</t>
+          <t>2026-09-14 07:00:00</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2921,7 +2924,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>FO Cut</t>
+          <t>prueba</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2931,12 +2934,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0130373</t>
+          <t>0130387</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0130373_LM_Carabayllo</t>
+          <t>0130387_LM_Lurin</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2951,12 +2954,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>21:57:39</t>
+          <t>16:38:45</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2971,7 +2974,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>PUENTE PIEDRA</t>
+          <t>LURIN</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2981,12 +2984,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Edgar Soto</t>
+          <t>Álvaro Ballarta</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2026-09-12 17:35:25</t>
+          <t>2026-09-13 19:09:30</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2996,15 +2999,9 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Operator: user:Jpachecom.cobra
-Complete time: 
-Description: 
-Operator: user:gvivanco.cobra
-Complete time: 
-Description: 
-Operator: user:Boris.Chivilchez
-Complete time: 2026-09-13 09:52:24
-Description: hilo roto en inicio de buffer</t>
+          <t>Operator: user:bcastillod
+Complete time: 2026-09-14 06:57:02
+Description: hilo partido, en mufa</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -3024,7 +3021,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>GERSON ANDRE VIVANCO DIESTRA</t>
+          <t>ANDY JAVIER RODAS VILLAJUAN</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -3034,17 +3031,17 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-09-13 09:52:26</t>
+          <t>2026-09-14 06:57:03</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2026-09-13 09:52:51</t>
+          <t>2026-09-14 06:57:41</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2026-09-13 09:52:53</t>
+          <t>2026-09-14 06:57:43</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -3071,32 +3068,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CM-20260912-00000224</t>
+          <t>CM-20260913-00000226</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INC-20260912-00006175</t>
+          <t>INC-20260913-00004824</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-09-12 16:23:51</t>
+          <t>2026-09-13 15:46:30</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14 14:22:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14 14:22:00</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3106,7 +3103,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t/>
+          <t>FO Cut</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -3116,17 +3113,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0135592</t>
+          <t>013253025</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0135592_LM_Ucayali_America</t>
+          <t>013253025_LM_PS_UniversidadTecLimaSur</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -3136,12 +3133,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>22:47:31</t>
+          <t>20:00:17</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -3156,22 +3153,22 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>unscheduled</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Edgar Soto</t>
+          <t>Álvaro Ballarta</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2026-09-12 16:45:33</t>
+          <t>2026-09-13 15:47:58</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -3181,7 +3178,9 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t>Operator: user:Boris.Chivilchez
+Complete time: 2026-09-14 14:17:43
+Description: HILO QUEBRADO EN MUFA POR MANIPULACIÓN DE TERCERO</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -3196,12 +3195,12 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>close</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t/>
+          <t>JHONATAN VICENTE ANASTACIO SAIRUTUPAC</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -3211,17 +3210,17 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14 14:17:45</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14 14:18:54</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14 14:18:57</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -3231,7 +3230,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t/>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -3248,32 +3247,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CM-20260912-00000212</t>
+          <t>CM-20260913-00000204</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>INC-20260912-00004906</t>
+          <t>INC-20260913-00004410</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-12 13:42:51</t>
+          <t>2026-09-13 14:26:48</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14 11:42:00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-12 18:22:05</t>
+          <t>2026-09-14 11:42:00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3283,7 +3282,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t/>
+          <t>FO Cut</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -3293,17 +3292,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0135774</t>
+          <t>0136114</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0135774_LM_Lima_Centro</t>
+          <t>0136114_LM_Jesus_Redentor</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -3318,7 +3317,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>00:03:03</t>
+          <t>21:20:43</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -3333,22 +3332,22 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>unscheduled</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Edgar Soto</t>
+          <t>Yoshua Quispe</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2026-09-12 15:30:01</t>
+          <t>2026-09-13 14:27:32</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -3358,7 +3357,9 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t xml:space="preserve">Operator: user:Yuliza.Jaimes
+Complete time: 2026-09-14 11:37:33
+Description: hilo cortado </t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -3373,12 +3374,12 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>close</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t/>
+          <t>GERSON ANDRE VIVANCO DIESTRA</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -3388,17 +3389,17 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14 11:37:35</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14 11:38:53</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14 11:38:55</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -3413,899 +3414,10 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CM-20260912-00000036</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>INC-20260912-00001099</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2026-09-12 03:53:39</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>772874247-The distribute fiber is broken or the OLT cannot receive expected optical signals from the ONT(LOSi LOBi)</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0135588</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0135588_LM_Trenemann</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>CAIDA</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>11:37:05</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>unscheduled</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Edgar Soto</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>2026-09-12 03:55:59</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CM-20260911-00000308</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>INC-20260911-00006754</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2026-09-11 19:31:09</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2507160001-ETH_LOS_CAIDA</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>0135588</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0135588_LM_Trenemann</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>CAIDA</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>19:41:08</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>unscheduled</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Edgar Soto</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>2026-09-11 19:51:56</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>CM-20260911-00000307</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>INC-20260911-00006754</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2026-09-11 19:31:09</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2507160006-ETH_LOS_Caida</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>0135588</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0135588_LM_Trenemann</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>CAIDA</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>19:42:02</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>unscheduled</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Edgar Soto</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>2026-09-11 19:51:02</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>CM-20260911-00000271</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>INC-20260911-00005217</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2026-09-11 17:56:51</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-09-12 13:18:00</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-09-12 13:18:00</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>10819-Hardware Fault</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>0130238</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0130238_LM_Mello_Franco</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>ENTORNO_FALLA EQ/GESTION</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>21:33:13</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>JESUS MARIA</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Yoshua Quispe</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>2026-09-11 17:59:51</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Operator: user:Boris.Chivilchez
-Complete time: 2026-09-12 13:12:27
-Description: se hizo descartes en mufa principal, hilos ok </t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>close</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>GERSON ANDRE VIVANCO DIESTRA</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2026-09-12 13:12:29</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>2026-09-12 13:14:48</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>2026-09-12 13:14:50</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>CM-20260911-00000266</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>INC-20260911-00006018</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2026-09-11 17:45:41</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-09-13 11:22:00</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-09-13 11:22:00</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>235-ETH_LOS</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>FO Cut</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>0130387</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0130387_LM_Lurin</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>CORTE</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>21:44:30</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>LURIN</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Álvaro Ballarta</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>2026-09-11 17:48:34</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Operator: user:bcastillod
-Complete time: 2026-09-13 11:18:58
-Description: NO Observación: SE llega a cordenadas brindadas por oym, se realiza revisión de mufa y se encuentra hilo roto al raz del buffer, hilo afectado es el nr 33 con dirección al cliente, se buscan hilos para realizar el cambio y se ubica hilo 30 que completa ruta sin atenuacion a siguiente mufa, se fusiona y se realiza el cambio de hilo entre mufa y mufa.</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>close</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>JUAN JOSE CARRION QUISPE</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>2026-09-13 11:18:59</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>2026-09-13 11:19:58</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>2026-09-13 11:19:59</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
         <is>
           <t/>
         </is>
